--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(1).xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11715"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（上）" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="470">
   <si>
     <t>ID</t>
   </si>
@@ -80,6 +85,9 @@
   </si>
   <si>
     <t>二层的楼道很长，逼仄的走廊将你们的影子压成窄窄的一条，拖在积灰的地板上，像两只在试管中穿行的蝌蚪。</t>
+  </si>
+  <si>
+    <t>1 enhanced alex-morgan-dark-suspense-thriller</t>
   </si>
   <si>
     <t>false</t>
@@ -439,6 +447,9 @@
     <t>话音未落，他的声音戛然而止，捏着布料的手指猛地收紧，仿佛眼睛里扎进了一根锋利的刺，将他死死钉在原地——</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=30</t>
   </si>
   <si>
@@ -455,6 +466,9 @@
   </si>
   <si>
     <t>凑近一瞧，一个数字浮现在了病服的胸口位置——236。</t>
+  </si>
+  <si>
+    <t>4 enhanced leberch-spooky-piano</t>
   </si>
   <si>
     <t>bgfade(sntzm_david313-315(1)_34,1)</t>
@@ -917,6 +931,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>playsfx(Electric)&amp;loadScript(</t>
     </r>
     <r>
@@ -949,7 +968,7 @@
     <t>45</t>
   </si>
   <si>
-    <t>你回忆起与这名同伴此前所共度的时光，回想起那些刺激、惊险，却又将你们推上同一只酒桌的任务。作为一名在任务中救过你无数次，也在职场中提供过诸多帮助的前辈。</t>
+    <t>你回忆起与这名同伴此前所共度的时光，回想起那些刺激、惊险，却又将你们推上同一只酒桌的任务。</t>
   </si>
   <si>
     <t>72</t>
@@ -1016,6 +1035,9 @@
   </si>
   <si>
     <t>就在这时，窗户突然传来一阵细微的抖动，准确来说是你们靠着的那一堵墙，像是有什么东西在上面黏腻地爬行。</t>
+  </si>
+  <si>
+    <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
     <t>shake(screen,2,2)</t>
@@ -1153,7 +1175,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>charfadeout(L,1)&amp;loadScript(</t>
+      <t>parallel(playsfx(Electric);charfadeout(L,1))&amp;loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -2951,7 +2973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:12">
+    <row r="2" ht="45" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2977,21 +2999,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -3009,7 +3031,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -3024,12 +3046,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="40.5" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -3047,7 +3069,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -3062,12 +3084,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3085,7 +3107,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -3100,12 +3122,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3123,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3138,12 +3160,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="55.5" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3161,7 +3183,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3176,15 +3198,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -3199,7 +3221,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3214,21 +3236,21 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3237,7 +3259,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3249,15 +3271,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3266,7 +3288,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3275,7 +3297,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3287,18 +3309,18 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -3313,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3328,21 +3350,21 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3351,7 +3373,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3363,15 +3385,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:12">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3380,7 +3402,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3389,7 +3411,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3404,21 +3426,21 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3427,7 +3449,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3442,12 +3464,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="55.5" spans="1:12">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3456,7 +3478,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3465,7 +3487,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3477,15 +3499,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="27" spans="1:12">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3503,7 +3525,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3518,12 +3540,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="70.5" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3541,7 +3563,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3553,12 +3575,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="57" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3576,7 +3598,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3591,12 +3613,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3614,7 +3636,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3629,12 +3651,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:12">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3652,7 +3674,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3664,15 +3686,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="55.5" spans="1:12">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3690,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3705,12 +3727,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3728,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3740,12 +3762,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3763,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3775,15 +3797,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3801,7 +3823,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3816,12 +3838,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3839,7 +3861,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3854,12 +3876,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3877,7 +3899,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3892,12 +3914,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:12">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3915,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3930,21 +3952,21 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:12">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3953,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3965,15 +3987,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:12">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3982,7 +4004,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3991,30 +4013,30 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -4029,7 +4051,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -4044,12 +4066,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" ht="28.5" spans="1:12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" ht="45" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4067,30 +4089,30 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -4105,14 +4127,11 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
@@ -4120,12 +4139,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4143,7 +4162,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4158,12 +4177,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="27" spans="1:12">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4181,7 +4200,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4196,21 +4215,21 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:12">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4219,7 +4238,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4231,24 +4250,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4257,7 +4276,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4272,12 +4291,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="42" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4286,7 +4305,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4295,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4307,15 +4326,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4333,7 +4352,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4348,12 +4367,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:12">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4383,15 +4402,15 @@
         <v>15</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4409,7 +4428,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4424,12 +4443,12 @@
         <v>15</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4447,7 +4466,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4459,15 +4478,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4485,7 +4504,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4500,15 +4519,15 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -4523,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4538,15 +4557,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="42" spans="1:12">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4561,7 +4580,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4576,12 +4595,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4599,7 +4618,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4614,15 +4633,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4637,7 +4656,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4652,12 +4671,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4675,7 +4694,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4690,21 +4709,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="30" spans="1:12">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4713,7 +4732,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4725,24 +4744,24 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="42" spans="1:12">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4751,7 +4770,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4766,12 +4785,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4780,7 +4799,7 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4789,7 +4808,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4804,21 +4823,21 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="55.5" spans="1:12">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4827,7 +4846,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4842,12 +4861,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="55.5" spans="1:12">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4856,7 +4875,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4865,7 +4884,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4877,18 +4896,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4903,7 +4922,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4918,21 +4937,21 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="42" spans="1:12">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4941,7 +4960,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4953,15 +4972,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4970,7 +4989,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4979,7 +4998,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4994,21 +5013,21 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="42" spans="1:12">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -5017,7 +5036,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -5032,12 +5051,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -5046,7 +5065,7 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5055,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5067,15 +5086,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L57" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="72" spans="1:12">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5093,7 +5112,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5108,12 +5127,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5131,7 +5150,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5146,12 +5165,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5169,7 +5188,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5184,12 +5203,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5207,7 +5226,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5222,21 +5241,21 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5245,7 +5264,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5257,15 +5276,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" ht="54" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5274,7 +5293,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5283,7 +5302,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5295,15 +5314,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5321,14 +5340,11 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
       </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
       <c r="J64" t="s">
         <v>15</v>
       </c>
@@ -5336,12 +5352,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" ht="67.5" spans="1:12">
       <c r="A65" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5359,13 +5375,13 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="J65" t="s">
         <v>15</v>
@@ -5374,12 +5390,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5397,7 +5413,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5409,15 +5425,15 @@
         <v>15</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L66" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5435,7 +5451,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5450,12 +5466,12 @@
         <v>15</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="68" ht="54" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5472,8 +5488,8 @@
       <c r="F68" t="s">
         <v>15</v>
       </c>
-      <c r="G68" t="s">
-        <v>224</v>
+      <c r="G68" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5488,12 +5504,12 @@
         <v>15</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5511,7 +5527,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5526,12 +5542,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" ht="27" spans="1:12">
       <c r="A70" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5549,7 +5565,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5564,12 +5580,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" ht="67.5" spans="1:12">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5587,7 +5603,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5599,15 +5615,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L71" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5625,7 +5641,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5640,12 +5656,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5663,14 +5679,11 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
       </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
       <c r="J73" t="s">
         <v>15</v>
       </c>
@@ -5678,21 +5691,21 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5701,27 +5714,27 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5730,7 +5743,7 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5739,7 +5752,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5751,15 +5764,15 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L75" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5777,27 +5790,27 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
       </c>
       <c r="I76" t="s">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="J76" t="s">
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="L76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" ht="67.5" spans="1:12">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5815,7 +5828,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5824,18 +5837,18 @@
         <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L77" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5850,7 +5863,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5865,12 +5878,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" ht="54" spans="1:12">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5888,7 +5901,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5900,15 +5913,15 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L79" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5926,7 +5939,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5941,12 +5954,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81" ht="27" spans="1:12">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5964,7 +5977,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5976,15 +5989,15 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L81" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:12">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6002,7 +6015,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6017,12 +6030,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" ht="40.5" spans="1:12">
       <c r="A83" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6040,7 +6053,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6055,15 +6068,15 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -6078,7 +6091,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6093,12 +6106,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6116,7 +6129,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6131,21 +6144,21 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -6154,7 +6167,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6166,15 +6179,15 @@
         <v>15</v>
       </c>
       <c r="K86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L86" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6183,7 +6196,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -6192,30 +6205,27 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
       </c>
-      <c r="I87" t="s">
-        <v>15</v>
-      </c>
       <c r="J87" t="s">
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L87" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>280</v>
-      </c>
-      <c r="B88" t="s">
-        <v>13</v>
+        <v>284</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6230,13 +6240,13 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="J88" t="s">
         <v>15</v>
@@ -6245,12 +6255,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6268,7 +6278,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6283,21 +6293,21 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="90" ht="40.5" spans="1:12">
       <c r="A90" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6306,7 +6316,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6318,15 +6328,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L90" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" ht="40.5" spans="1:12">
       <c r="A91" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6335,7 +6345,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6344,7 +6354,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6356,10 +6366,10 @@
         <v>15</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L91" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -6380,106 +6390,106 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:2">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" ht="60" spans="1:2">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" ht="75" spans="1:2">
       <c r="A13" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -6501,616 +6511,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F7" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D9" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C10" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F10" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E11" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F11" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D12" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F12" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C14" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E14" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C15" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D15" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E15" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F15" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C16" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D16" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E16" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F16" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B17" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C17" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D17" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E17" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F17" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C18" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D18" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E18" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F18" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B19" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C19" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D19" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E19" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F19" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B20" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C20" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D20" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E20" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F20" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B21" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D21" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E21" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F21" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B22" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C22" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D22" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E22" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F22" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B23" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C23" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E23" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F23" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C24" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D24" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E24" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B25" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C25" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D25" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E25" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F25" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B26" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D26" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E26" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F26" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B27" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C27" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D27" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E27" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F27" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B28" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C28" t="s">
+        <v>453</v>
+      </c>
+      <c r="D28" t="s">
         <v>449</v>
       </c>
-      <c r="D28" t="s">
-        <v>445</v>
-      </c>
       <c r="E28" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F28" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B29" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C29" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D29" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E29" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F29" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B30" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D30" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E30" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F30" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B31" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C31" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D31" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11715"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线313-315（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="470">
   <si>
     <t>ID</t>
   </si>
@@ -93,7 +93,7 @@
     <t>false</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david313-315(1)_1,1)</t>
+    <t>bgfade(sntzm_david313-315(1)_1,1)&amp;unlockmusic(Music1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=0</t>
@@ -471,7 +471,7 @@
     <t>4 enhanced leberch-spooky-piano</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david313-315(1)_34,1)</t>
+    <t>bgfade(sntzm_david313-315(1)_34,1)&amp;unlockmusic(Music4)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=32</t>
@@ -637,78 +637,7 @@
     <t>bgfade(sntzm_david313-315(1)_46,1)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>源类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">=type:txt_pb; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">=42; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>选项</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>备注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>现在赶时间要紧</t>
-    </r>
+    <t>源类型=type:txt_pb; 层级=42; 选项/备注=现在赶时间要紧;tag=追问</t>
   </si>
   <si>
     <t>47</t>
@@ -880,12 +809,6 @@
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=61</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=62</t>
   </si>
   <si>
     <t>67</t>
@@ -971,6 +894,9 @@
     <t>你回忆起与这名同伴此前所共度的时光，回想起那些刺激、惊险，却又将你们推上同一只酒桌的任务。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=42; 选项/备注=现在赶时间要紧;tag=忽视</t>
+  </si>
+  <si>
     <t>72</t>
   </si>
   <si>
@@ -1040,7 +966,7 @@
     <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
-    <t>shake(screen,2,2)</t>
+    <t>shake(screen,2,2)&amp;unlockmusic(Music5)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=50</t>
@@ -1143,6 +1069,9 @@
   </si>
   <si>
     <t>我们得赶紧离开这儿......</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=62</t>
   </si>
   <si>
     <t>92</t>
@@ -2922,7 +2851,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5206,50 +5135,50 @@
         <v>205</v>
       </c>
     </row>
-    <row r="61" ht="27" spans="1:12">
+    <row r="61" ht="40.5" spans="1:12">
       <c r="A61" t="s">
         <v>206</v>
       </c>
       <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
+        <v>42</v>
+      </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>44</v>
+      </c>
+      <c r="L61" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" ht="54" spans="1:12">
+      <c r="A62" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" t="s">
         <v>13</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>204</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="62" ht="40.5" spans="1:12">
-      <c r="A62" t="s">
-        <v>208</v>
-      </c>
-      <c r="B62" t="s">
-        <v>41</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5264,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5276,15 +5205,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="63" ht="54" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5293,7 +5222,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5302,27 +5231,24 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
       </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
       <c r="J63" t="s">
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="64" ht="40.5" spans="1:12">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" ht="67.5" spans="1:12">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5340,11 +5266,14 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
       </c>
+      <c r="I64" t="s">
+        <v>108</v>
+      </c>
       <c r="J64" t="s">
         <v>15</v>
       </c>
@@ -5352,12 +5281,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" ht="67.5" spans="1:12">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5375,27 +5304,27 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="J65" t="s">
         <v>15</v>
       </c>
-      <c r="K65" t="s">
-        <v>15</v>
+      <c r="K65" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="L65" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="66" ht="40.5" spans="1:12">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5413,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5424,14 +5353,14 @@
       <c r="J66" t="s">
         <v>15</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="L66" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
         <v>224</v>
       </c>
@@ -5450,7 +5379,7 @@
       <c r="F67" t="s">
         <v>15</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="2" t="s">
         <v>225</v>
       </c>
       <c r="H67" t="s">
@@ -5466,12 +5395,12 @@
         <v>15</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5488,8 +5417,8 @@
       <c r="F68" t="s">
         <v>15</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>227</v>
+      <c r="G68" t="s">
+        <v>228</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5503,13 +5432,13 @@
       <c r="K68" t="s">
         <v>15</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" ht="40.5" spans="1:12">
+      <c r="L68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5527,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5542,12 +5471,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" ht="27" spans="1:12">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" ht="67.5" spans="1:12">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5565,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5577,15 +5506,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>234</v>
       </c>
       <c r="L70" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" ht="67.5" spans="1:12">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5603,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5615,15 +5544,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>235</v>
+        <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>236</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5641,14 +5570,11 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
       </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
       <c r="J72" t="s">
         <v>15</v>
       </c>
@@ -5656,50 +5582,53 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="73" ht="40.5" spans="1:12">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
+        <v>42</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
+        <v>242</v>
+      </c>
+      <c r="H73" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" t="s">
+        <v>108</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="74" ht="67.5" spans="1:12">
+      <c r="A74" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" t="s">
         <v>13</v>
-      </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>15</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" t="s">
-        <v>240</v>
-      </c>
-      <c r="H73" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>15</v>
-      </c>
-      <c r="L73" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" ht="30" spans="1:12">
-      <c r="A74" t="s">
-        <v>242</v>
-      </c>
-      <c r="B74" t="s">
-        <v>41</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5714,27 +5643,27 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L74" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="75" ht="67.5" spans="1:12">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5743,7 +5672,7 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5752,27 +5681,27 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="J75" t="s">
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>48</v>
+        <v>250</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="76" ht="40.5" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="76" ht="67.5" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5790,66 +5719,66 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
       </c>
       <c r="I76" t="s">
-        <v>250</v>
-      </c>
-      <c r="J76" t="s">
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L76" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="77" ht="67.5" spans="1:12">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B77" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>256</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="78" ht="54" spans="1:12">
+      <c r="A78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
         <v>13</v>
       </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>254</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>255</v>
-      </c>
-      <c r="L77" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" t="s">
-        <v>256</v>
-      </c>
-      <c r="B78" t="s">
-        <v>37</v>
-      </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
@@ -5863,7 +5792,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5875,15 +5804,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="L78" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="79" ht="54" spans="1:12">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5901,7 +5830,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5913,15 +5842,15 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>261</v>
+        <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="80" ht="40.5" spans="1:12">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="80" ht="27" spans="1:12">
       <c r="A80" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5939,7 +5868,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5951,15 +5880,15 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
       <c r="L80" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="81" ht="27" spans="1:12">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5977,7 +5906,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5989,15 +5918,15 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="82" ht="54" spans="1:12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" ht="40.5" spans="1:12">
       <c r="A82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6015,7 +5944,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6030,54 +5959,54 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="83" ht="40.5" spans="1:12">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B83" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>274</v>
+      </c>
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="84" ht="27" spans="1:12">
+      <c r="A84" t="s">
+        <v>276</v>
+      </c>
+      <c r="B84" t="s">
         <v>13</v>
       </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
-        <v>272</v>
-      </c>
-      <c r="H83" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" t="s">
-        <v>15</v>
-      </c>
-      <c r="K83" t="s">
-        <v>15</v>
-      </c>
-      <c r="L83" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" t="s">
-        <v>274</v>
-      </c>
-      <c r="B84" t="s">
-        <v>37</v>
-      </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
@@ -6091,7 +6020,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6106,53 +6035,53 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="85" ht="27" spans="1:12">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" ht="30" spans="1:12">
       <c r="A85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>279</v>
+      </c>
+      <c r="H85" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>44</v>
+      </c>
+      <c r="L85" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="86" ht="40.5" spans="1:12">
+      <c r="A86" t="s">
+        <v>281</v>
+      </c>
+      <c r="B86" t="s">
         <v>13</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" t="s">
-        <v>278</v>
-      </c>
-      <c r="H85" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" t="s">
-        <v>15</v>
-      </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
-      <c r="L85" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="86" ht="30" spans="1:12">
-      <c r="A86" t="s">
-        <v>279</v>
-      </c>
-      <c r="B86" t="s">
-        <v>41</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -6167,141 +6096,141 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
       </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
       <c r="J86" t="s">
         <v>15</v>
       </c>
       <c r="K86" t="s">
+        <v>48</v>
+      </c>
+      <c r="L86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>283</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" t="s">
+        <v>284</v>
+      </c>
+      <c r="H87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" t="s">
+        <v>108</v>
+      </c>
+      <c r="J87" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" t="s">
+        <v>15</v>
+      </c>
+      <c r="L87" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88" ht="27" spans="1:12">
+      <c r="A88" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s">
+        <v>287</v>
+      </c>
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>15</v>
+      </c>
+      <c r="L88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="89" ht="40.5" spans="1:12">
+      <c r="A89" t="s">
+        <v>289</v>
+      </c>
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>42</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
+        <v>290</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
         <v>44</v>
       </c>
-      <c r="L86" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="87" ht="40.5" spans="1:12">
-      <c r="A87" t="s">
-        <v>282</v>
-      </c>
-      <c r="B87" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" t="s">
-        <v>283</v>
-      </c>
-      <c r="H87" t="s">
-        <v>15</v>
-      </c>
-      <c r="J87" t="s">
-        <v>15</v>
-      </c>
-      <c r="K87" t="s">
-        <v>48</v>
-      </c>
-      <c r="L87" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" t="s">
-        <v>284</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" t="s">
-        <v>285</v>
-      </c>
-      <c r="H88" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>108</v>
-      </c>
-      <c r="J88" t="s">
-        <v>15</v>
-      </c>
-      <c r="K88" t="s">
-        <v>15</v>
-      </c>
-      <c r="L88" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="89" ht="27" spans="1:12">
-      <c r="A89" t="s">
-        <v>286</v>
-      </c>
-      <c r="B89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" t="s">
-        <v>287</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" t="s">
-        <v>15</v>
-      </c>
       <c r="L89" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" ht="40.5" spans="1:12">
       <c r="A90" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -6316,7 +6245,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6327,48 +6256,10 @@
       <c r="J90" t="s">
         <v>15</v>
       </c>
-      <c r="K90" t="s">
-        <v>44</v>
+      <c r="K90" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="L90" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="91" ht="40.5" spans="1:12">
-      <c r="A91" t="s">
-        <v>292</v>
-      </c>
-      <c r="B91" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" t="s">
-        <v>14</v>
-      </c>
-      <c r="D91" t="s">
-        <v>42</v>
-      </c>
-      <c r="E91" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" t="s">
-        <v>293</v>
-      </c>
-      <c r="H91" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" t="s">
-        <v>15</v>
-      </c>
-      <c r="J91" t="s">
-        <v>15</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="L91" t="s">
         <v>295</v>
       </c>
     </row>
